--- a/data/trans_orig/P16A_n_R3-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R3-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489310</t>
+          <t>489389</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>461824</t>
+          <t>462788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>955888</t>
+          <t>955831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>854</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>731079</t>
+          <t>731287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>619206</t>
+          <t>619105</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1353257</t>
+          <t>1353789</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360114</t>
+          <t>1360128</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12671</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631542</t>
+          <t>631541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637801</t>
+          <t>637803</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>677073</t>
+          <t>677128</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>686854</t>
+          <t>687595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1312912</t>
+          <t>1312421</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324484</t>
+          <t>1324405</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1776</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17957</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25301</t>
+          <t>25118</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>506805</t>
+          <t>506944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>518072</t>
+          <t>517371</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497685</t>
+          <t>497346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>510586</t>
+          <t>510508</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1009488</t>
+          <t>1009671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1026485</t>
+          <t>1026452</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30365</t>
+          <t>31056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38998</t>
+          <t>38308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>372173</t>
+          <t>372872</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>383464</t>
+          <t>383912</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>373621</t>
+          <t>372930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>391353</t>
+          <t>390964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>751698</t>
+          <t>752388</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>772374</t>
+          <t>773469</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>18913</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>15776</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35095</t>
+          <t>34063</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26691</t>
+          <t>24873</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49115</t>
+          <t>46132</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273311</t>
+          <t>273670</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286088</t>
+          <t>286219</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>307839</t>
+          <t>308871</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>326840</t>
+          <t>327158</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>586402</t>
+          <t>589385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>608826</t>
+          <t>610644</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>16130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34922</t>
+          <t>36081</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32652</t>
+          <t>32597</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59906</t>
+          <t>59109</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178982</t>
+          <t>180285</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>196686</t>
+          <t>197208</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>298986</t>
+          <t>297827</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>318913</t>
+          <t>317778</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>483885</t>
+          <t>484682</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>511139</t>
+          <t>511194</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36592</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64528</t>
+          <t>62924</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69379</t>
+          <t>71158</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108246</t>
+          <t>107516</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113981</t>
+          <t>113739</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>161115</t>
+          <t>160060</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3212015</t>
+          <t>3213619</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3239951</t>
+          <t>3239811</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3270951</t>
+          <t>3271681</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3309818</t>
+          <t>3308039</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6494626</t>
+          <t>6495681</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6541760</t>
+          <t>6542002</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,97 +3712,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7950</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7044</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>7066</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7150</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423186</t>
+          <t>422280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>877226</t>
+          <t>877310</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>14267</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10245</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>16985</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>675157</t>
+          <t>672820</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>600010</t>
+          <t>600125</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609368</t>
+          <t>609359</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1279170</t>
+          <t>1280357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1294816</t>
+          <t>1295463</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,82 +4413,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>10943</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5831</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>19087</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>15830</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>9604</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>26321</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>1,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10943</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5989</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>19788</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>15830</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>9488</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>25826</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668964</t>
+          <t>669792</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680809</t>
+          <t>680082</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,82 +4526,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>699907</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>691763</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>705019</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1376882</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1366391</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1383108</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>98,11%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>699907</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>691062</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>704861</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1376882</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1366886</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1383224</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14741</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>9651</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25746</t>
+          <t>26875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33767</t>
+          <t>35669</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>599876</t>
+          <t>598924</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612650</t>
+          <t>612537</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>590453</t>
+          <t>589324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>607538</t>
+          <t>606548</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1197049</t>
+          <t>1195147</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1215964</t>
+          <t>1216204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20451</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42251</t>
+          <t>41165</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24216</t>
+          <t>23879</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46465</t>
+          <t>46916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418600</t>
+          <t>418749</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428371</t>
+          <t>428386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>405549</t>
+          <t>406635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>427114</t>
+          <t>427349</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>830764</t>
+          <t>830313</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>853013</t>
+          <t>853350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26272</t>
+          <t>26031</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33450</t>
+          <t>33442</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59981</t>
+          <t>61154</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47047</t>
+          <t>45920</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77493</t>
+          <t>76972</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>283514</t>
+          <t>283755</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>301421</t>
+          <t>301489</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>294015</t>
+          <t>292842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>320546</t>
+          <t>320554</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>586289</t>
+          <t>586810</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>616735</t>
+          <t>617862</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>40642</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55020</t>
+          <t>53665</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86977</t>
+          <t>84939</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78297</t>
+          <t>78754</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115644</t>
+          <t>115814</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210448</t>
+          <t>209209</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>231841</t>
+          <t>232294</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>302002</t>
+          <t>304040</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>333959</t>
+          <t>335314</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>523186</t>
+          <t>523016</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>560533</t>
+          <t>560076</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,67%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45861</t>
+          <t>46500</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80691</t>
+          <t>81122</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154178</t>
+          <t>152290</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>205263</t>
+          <t>203778</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>205742</t>
+          <t>210195</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>271287</t>
+          <t>272328</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3346088</t>
+          <t>3345657</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3380918</t>
+          <t>3380279</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3353046</t>
+          <t>3354531</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3404131</t>
+          <t>3406019</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6713801</t>
+          <t>6712760</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6779346</t>
+          <t>6774893</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,97 +6691,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>813256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>815218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>584933</t>
+          <t>585185</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555073</t>
+          <t>555982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562639</t>
+          <t>562634</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1144657</t>
+          <t>1145417</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153079</t>
+          <t>1153074</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,82 +7377,82 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5825</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1878</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6596</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>654790</t>
+          <t>655561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1323804</t>
+          <t>1323811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29127</t>
+          <t>28543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29640</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>640630</t>
+          <t>637919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>619950</t>
+          <t>620534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>637788</t>
+          <t>638608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1265485</t>
+          <t>1264832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1283545</t>
+          <t>1283325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>21627</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22075</t>
+          <t>22222</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46490</t>
+          <t>45160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32994</t>
+          <t>32730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61645</t>
+          <t>59952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>456304</t>
+          <t>456291</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471337</t>
+          <t>471336</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>450359</t>
+          <t>451689</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>474774</t>
+          <t>474627</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>913122</t>
+          <t>914815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>941773</t>
+          <t>942037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31153</t>
+          <t>30457</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30786</t>
+          <t>31013</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55502</t>
+          <t>54998</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48154</t>
+          <t>48307</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78456</t>
+          <t>77640</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>303177</t>
+          <t>303873</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>321020</t>
+          <t>321431</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>322260</t>
+          <t>322764</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>346976</t>
+          <t>346749</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>633636</t>
+          <t>634452</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>663938</t>
+          <t>663785</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,22%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>30500</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43652</t>
+          <t>42999</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73856</t>
+          <t>73017</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61281</t>
+          <t>63168</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95634</t>
+          <t>97518</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>226526</t>
+          <t>226498</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242660</t>
+          <t>242148</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>326313</t>
+          <t>327152</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>356517</t>
+          <t>357170</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>561533</t>
+          <t>559649</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>595886</t>
+          <t>593999</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43049</t>
+          <t>42439</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>70937</t>
+          <t>71332</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>127474</t>
+          <t>130043</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>178651</t>
+          <t>183207</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>179161</t>
+          <t>181738</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>239935</t>
+          <t>242032</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3323413</t>
+          <t>3323018</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3351301</t>
+          <t>3351911</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3365891</t>
+          <t>3361335</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3417068</t>
+          <t>3414499</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6698957</t>
+          <t>6696860</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6759731</t>
+          <t>6757154</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,82 +9670,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1621</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8892</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1621</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7974</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1621</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305226</t>
+          <t>304308</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>703357</t>
+          <t>703323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415041</t>
+          <t>415074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504962</t>
+          <t>504336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>924817</t>
+          <t>923307</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>934401</t>
+          <t>934358</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14251</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25953</t>
+          <t>24569</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522087</t>
+          <t>521540</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533935</t>
+          <t>533932</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>577074</t>
+          <t>576730</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>587165</t>
+          <t>586968</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1102387</t>
+          <t>1103771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1118816</t>
+          <t>1118671</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36218</t>
+          <t>37638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30613</t>
+          <t>31656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60756</t>
+          <t>59745</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38938</t>
+          <t>39179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87278</t>
+          <t>87459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>851568</t>
+          <t>850148</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879046</t>
+          <t>879613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>652125</t>
+          <t>653136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>682268</t>
+          <t>681225</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1513389</t>
+          <t>1513208</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1561729</t>
+          <t>1561488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25592</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49652</t>
+          <t>50119</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71532</t>
+          <t>71873</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80631</t>
+          <t>80263</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111311</t>
+          <t>109995</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>535642</t>
+          <t>536811</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>476373</t>
+          <t>476032</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>498253</t>
+          <t>497786</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>997828</t>
+          <t>999144</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1028508</t>
+          <t>1028876</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31184</t>
+          <t>30965</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49057</t>
+          <t>49834</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32025</t>
+          <t>31188</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116946</t>
+          <t>117122</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>62702</t>
+          <t>57916</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150440</t>
+          <t>151453</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>319108</t>
+          <t>318331</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>336981</t>
+          <t>337200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>491422</t>
+          <t>491246</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>576343</t>
+          <t>577180</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>826093</t>
+          <t>825080</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>913831</t>
+          <t>918617</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42964</t>
+          <t>42423</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63470</t>
+          <t>62516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125618</t>
+          <t>126605</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152401</t>
+          <t>154560</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>174995</t>
+          <t>174737</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>210567</t>
+          <t>209368</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>219289</t>
+          <t>220243</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>239795</t>
+          <t>240336</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>273430</t>
+          <t>271271</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>300213</t>
+          <t>299226</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>498023</t>
+          <t>499222</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>533595</t>
+          <t>533853</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>123430</t>
+          <t>122552</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>183887</t>
+          <t>181536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264499</t>
+          <t>266250</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>364092</t>
+          <t>365936</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>421523</t>
+          <t>415423</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>536767</t>
+          <t>533785</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3275930</t>
+          <t>3278281</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3336387</t>
+          <t>3337265</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3348188</t>
+          <t>3346344</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3447781</t>
+          <t>3446030</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6635330</t>
+          <t>6638312</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6750574</t>
+          <t>6756674</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R3-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R3-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489389</t>
+          <t>489313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>462788</t>
+          <t>462800</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>955831</t>
+          <t>954966</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>863</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>731287</t>
+          <t>731087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>619105</t>
+          <t>619350</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1353789</t>
+          <t>1352981</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360128</t>
+          <t>1360119</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631541</t>
+          <t>631476</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637803</t>
+          <t>637792</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>677128</t>
+          <t>676790</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>687595</t>
+          <t>687594</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1312421</t>
+          <t>1312182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324405</t>
+          <t>1324375</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18296</t>
+          <t>18499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25118</t>
+          <t>23786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>506944</t>
+          <t>507086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>517371</t>
+          <t>518061</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497346</t>
+          <t>497143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>510508</t>
+          <t>510566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1009671</t>
+          <t>1011003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1026452</t>
+          <t>1026500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31056</t>
+          <t>30045</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17227</t>
+          <t>17527</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>38336</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>372872</t>
+          <t>371547</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>383912</t>
+          <t>383273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>372930</t>
+          <t>373941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>390964</t>
+          <t>391783</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>752388</t>
+          <t>752360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>773469</t>
+          <t>773169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>19062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15776</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34063</t>
+          <t>34812</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24873</t>
+          <t>25114</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46132</t>
+          <t>48463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273670</t>
+          <t>273521</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286219</t>
+          <t>286392</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>308871</t>
+          <t>308122</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>327158</t>
+          <t>326750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>589385</t>
+          <t>587054</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>610644</t>
+          <t>610403</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12675</t>
+          <t>12816</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29598</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>15580</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36081</t>
+          <t>34896</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32597</t>
+          <t>33273</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59109</t>
+          <t>59517</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>180285</t>
+          <t>180160</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>197208</t>
+          <t>197067</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297827</t>
+          <t>299012</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>317778</t>
+          <t>318328</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>484682</t>
+          <t>484274</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>511194</t>
+          <t>510518</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36732</t>
+          <t>36699</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62924</t>
+          <t>66042</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71158</t>
+          <t>71073</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107516</t>
+          <t>109134</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113739</t>
+          <t>114323</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>159065</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3213619</t>
+          <t>3210501</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3239811</t>
+          <t>3239844</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3271681</t>
+          <t>3270063</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3308039</t>
+          <t>3308124</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6495681</t>
+          <t>6496676</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6542002</t>
+          <t>6541418</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>422280</t>
+          <t>422825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>877310</t>
+          <t>877265</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>13567</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>10483</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16985</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>672820</t>
+          <t>673520</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>600125</t>
+          <t>599772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609359</t>
+          <t>609365</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1280357</t>
+          <t>1278427</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1295463</t>
+          <t>1294786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>19141</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>24946</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>669792</t>
+          <t>668907</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680082</t>
+          <t>680800</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>691763</t>
+          <t>691709</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>705019</t>
+          <t>704907</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1366391</t>
+          <t>1367766</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1383108</t>
+          <t>1383822</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>14697</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26875</t>
+          <t>25135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35669</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>598924</t>
+          <t>599920</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612537</t>
+          <t>612576</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>589324</t>
+          <t>591064</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>606548</t>
+          <t>606572</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1195147</t>
+          <t>1197527</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1216204</t>
+          <t>1217097</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41165</t>
+          <t>40975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23879</t>
+          <t>24214</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46916</t>
+          <t>46544</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418749</t>
+          <t>419420</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428386</t>
+          <t>428378</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>406635</t>
+          <t>406825</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>427349</t>
+          <t>427831</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>830313</t>
+          <t>830685</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>853350</t>
+          <t>853015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26031</t>
+          <t>26046</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33442</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61154</t>
+          <t>59078</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45920</t>
+          <t>46116</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76972</t>
+          <t>77187</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>283755</t>
+          <t>283740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>301489</t>
+          <t>301548</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>292842</t>
+          <t>294918</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>320554</t>
+          <t>321035</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>586810</t>
+          <t>586595</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>617862</t>
+          <t>617666</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>18356</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40642</t>
+          <t>42209</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53665</t>
+          <t>54917</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84939</t>
+          <t>86636</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78754</t>
+          <t>76775</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115814</t>
+          <t>113659</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>209209</t>
+          <t>207642</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>232294</t>
+          <t>231495</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>304040</t>
+          <t>302343</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>335314</t>
+          <t>334062</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>523016</t>
+          <t>525171</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>560076</t>
+          <t>562055</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46500</t>
+          <t>46738</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81122</t>
+          <t>84898</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>152290</t>
+          <t>151751</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203778</t>
+          <t>205189</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>210195</t>
+          <t>209642</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>272328</t>
+          <t>270618</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3345657</t>
+          <t>3341881</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3380279</t>
+          <t>3380041</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3354531</t>
+          <t>3353120</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3406019</t>
+          <t>3406558</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6712760</t>
+          <t>6714470</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6774893</t>
+          <t>6775446</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>968</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>585185</t>
+          <t>585642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555982</t>
+          <t>556003</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562634</t>
+          <t>562638</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1145417</t>
+          <t>1144551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153074</t>
+          <t>1153072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>655561</t>
+          <t>655264</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1323811</t>
+          <t>1324225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28543</t>
+          <t>27942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30293</t>
+          <t>29925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>637919</t>
+          <t>640605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>620534</t>
+          <t>621135</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>638608</t>
+          <t>638184</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1264832</t>
+          <t>1265200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1283325</t>
+          <t>1283464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21627</t>
+          <t>22100</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22222</t>
+          <t>22636</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45160</t>
+          <t>45648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32730</t>
+          <t>33078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59952</t>
+          <t>59566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>456291</t>
+          <t>455818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471336</t>
+          <t>471374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>451689</t>
+          <t>451201</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>474627</t>
+          <t>474213</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>914815</t>
+          <t>915201</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>942037</t>
+          <t>941689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30457</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31013</t>
+          <t>29955</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54998</t>
+          <t>55257</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48307</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77640</t>
+          <t>79165</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>303873</t>
+          <t>305166</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>321431</t>
+          <t>321474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>322764</t>
+          <t>322505</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>346749</t>
+          <t>347807</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>634452</t>
+          <t>632927</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>663785</t>
+          <t>664092</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30500</t>
+          <t>31065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42999</t>
+          <t>42873</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73017</t>
+          <t>75134</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63168</t>
+          <t>62250</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97518</t>
+          <t>96002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>226498</t>
+          <t>225933</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242148</t>
+          <t>242046</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>327152</t>
+          <t>325035</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>357170</t>
+          <t>357296</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>559649</t>
+          <t>561165</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>593999</t>
+          <t>594917</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42439</t>
+          <t>41897</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>71332</t>
+          <t>72025</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130043</t>
+          <t>129772</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>183207</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>181738</t>
+          <t>182546</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>242032</t>
+          <t>241787</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3323018</t>
+          <t>3322325</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3351911</t>
+          <t>3352453</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3361335</t>
+          <t>3366846</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3414499</t>
+          <t>3414770</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6696860</t>
+          <t>6697105</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6757154</t>
+          <t>6756346</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,27 +9813,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>311579</t>
+          <t>360480</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304308</t>
+          <t>352337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>711566</t>
+          <t>768273</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>703323</t>
+          <t>758443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421071</t>
+          <t>474348</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415074</t>
+          <t>467863</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,27 +10156,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>509993</t>
+          <t>499742</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504336</t>
+          <t>495348</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>931065</t>
+          <t>974089</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>923307</t>
+          <t>967748</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>934358</t>
+          <t>977447</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14798</t>
+          <t>13946</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>10874</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15272</t>
+          <t>17708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,17 +10421,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24569</t>
+          <t>26554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>530057</t>
+          <t>614383</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521540</t>
+          <t>606891</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533932</t>
+          <t>618505</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>582650</t>
+          <t>612319</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>576730</t>
+          <t>605485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>586968</t>
+          <t>616777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,17 +10534,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1112706</t>
+          <t>1226701</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1103771</t>
+          <t>1217475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1118671</t>
+          <t>1233231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22018</t>
+          <t>23326</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37638</t>
+          <t>37016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,67 +10729,67 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42287</t>
+          <t>40522</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31656</t>
+          <t>30801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59745</t>
+          <t>52039</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>7,06%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>63847</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>51173</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>80882</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>4,44%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>64304</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>39179</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>87459</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>865768</t>
+          <t>677291</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>850148</t>
+          <t>663601</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879613</t>
+          <t>685338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,67 +10842,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>670594</t>
+          <t>696364</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>653136</t>
+          <t>684847</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681225</t>
+          <t>706085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>95,82%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1373657</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1356622</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1386331</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>95,56%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1536363</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1513208</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1561488</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>34179</t>
+          <t>36132</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>25824</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45636</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>60250</t>
+          <t>67858</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50119</t>
+          <t>56557</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71873</t>
+          <t>81065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>94429</t>
+          <t>103991</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80263</t>
+          <t>88841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109995</t>
+          <t>123231</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>527055</t>
+          <t>573214</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>515598</t>
+          <t>560973</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>536811</t>
+          <t>583522</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>487655</t>
+          <t>540997</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>476032</t>
+          <t>527790</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>497786</t>
+          <t>552298</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1014710</t>
+          <t>1114211</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>999144</t>
+          <t>1094971</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1028876</t>
+          <t>1129361</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>39544</t>
+          <t>40953</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30965</t>
+          <t>31057</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49834</t>
+          <t>49953</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>74281</t>
+          <t>81986</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31188</t>
+          <t>70885</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117122</t>
+          <t>93414</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>113825</t>
+          <t>122939</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57916</t>
+          <t>109237</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>151453</t>
+          <t>139311</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>328621</t>
+          <t>366127</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>318331</t>
+          <t>357127</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>337200</t>
+          <t>376023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>534087</t>
+          <t>357180</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>491246</t>
+          <t>345752</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>577180</t>
+          <t>368281</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>862708</t>
+          <t>723307</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>825080</t>
+          <t>706935</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>918617</t>
+          <t>737009</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>52039</t>
+          <t>58008</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42423</t>
+          <t>46819</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62516</t>
+          <t>70519</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>139915</t>
+          <t>151349</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>126605</t>
+          <t>137297</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>154560</t>
+          <t>165989</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>191954</t>
+          <t>209358</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>174737</t>
+          <t>191727</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>209368</t>
+          <t>228178</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>230720</t>
+          <t>252190</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>220243</t>
+          <t>239679</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>240336</t>
+          <t>263379</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>285916</t>
+          <t>313260</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>271271</t>
+          <t>298620</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>299226</t>
+          <t>327312</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>516636</t>
+          <t>565449</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>499222</t>
+          <t>546629</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>533853</t>
+          <t>583080</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>156537</t>
+          <t>167415</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>122552</t>
+          <t>146648</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>181536</t>
+          <t>190405</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>329805</t>
+          <t>356614</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>266250</t>
+          <t>331277</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>365936</t>
+          <t>390470</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>486342</t>
+          <t>524028</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>415423</t>
+          <t>488369</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>533785</t>
+          <t>561122</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3303280</t>
+          <t>3365347</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3278281</t>
+          <t>3342357</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3337265</t>
+          <t>3386114</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3382475</t>
+          <t>3380340</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3346344</t>
+          <t>3346484</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3446030</t>
+          <t>3405677</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6685755</t>
+          <t>6745688</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6638312</t>
+          <t>6708594</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6756674</t>
+          <t>6781347</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
